--- a/outputs/tables/TableS12_SA-axis-patterning-genes.xlsx
+++ b/outputs/tables/TableS12_SA-axis-patterning-genes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachelsmith/Documents/Postdoc/projects/ASD-rarevar-annot/outputs/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71CF1BC-8E45-DD4D-B6FE-99765E9450E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DD64E7-D8E1-4545-A2D2-725AFCC05CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7620" yWindow="-17180" windowWidth="20200" windowHeight="16320" xr2:uid="{1C02299E-6F63-1345-B67A-E93A7852DBCE}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17580" xr2:uid="{1C02299E-6F63-1345-B67A-E93A7852DBCE}"/>
   </bookViews>
   <sheets>
     <sheet name="S_A (Tsyporin et al 2026)" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
     <t>Gene</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Association/pericentral</t>
   </si>
   <si>
-    <t>MEIS2</t>
-  </si>
-  <si>
     <t>Role in Tsyporin 2026</t>
   </si>
   <si>
@@ -150,12 +147,6 @@
   </si>
   <si>
     <t>appears in expression panels only (shared Satb2/Zbtb18-cKO DEG down); deep-layer TF, pole not specified</t>
-  </si>
-  <si>
-    <t>RA-regulated  Af (association) marker; up with RA in organoids; lack regional patterns in Zbtb18-cKO.</t>
-  </si>
-  <si>
-    <t>risk gene; MEIS3 is MORPH regulon TF</t>
   </si>
   <si>
     <t>risk gene; FOXP2 is MORPH regulon TF</t>
@@ -576,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F113FC2D-59FE-B040-B65F-9BBA1B54DD6A}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
@@ -590,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D1" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1</v>
@@ -607,13 +598,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
@@ -624,13 +615,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
@@ -638,16 +629,16 @@
     </row>
     <row r="4" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
@@ -655,67 +646,67 @@
     </row>
     <row r="5" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
@@ -723,103 +714,86 @@
     </row>
     <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
         <v>7</v>
       </c>
     </row>
